--- a/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Inventario Diario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Limpieza Semanal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FIFO Semanal" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Mantenimiento Mensual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario Diario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Inventario Diario'!$A$1:$F$40</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Limpieza Semanal'!$A$1:$G$20</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'FIFO Semanal'!$A$1:$G$20</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Mantenimiento Mensual'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +88,11 @@
       <color rgb="00228B22"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -144,50 +150,66 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -547,15 +569,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -563,6 +586,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -570,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -584,6 +609,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -591,8 +617,33 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -601,20 +652,20 @@
   <sheetPr>
     <tabColor rgb="00FF6600"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="10"/>
-    <col customWidth="1" max="3" min="3" width="10"/>
-    <col customWidth="1" max="4" min="4" width="10"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inventario Diario — Stock de Producción Hamburguesería</t>
@@ -628,6 +679,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -1346,6 +1398,7 @@
       </c>
       <c r="F38" s="8" t="n"/>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -1356,8 +1409,8 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A19:F19"/>
@@ -1365,7 +1418,16 @@
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1379,16 +1441,16 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Limpieza Profunda Semanal</t>
@@ -1402,10 +1464,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1430,7 +1493,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1447,10 +1510,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -1476,10 +1537,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -1505,10 +1564,8 @@
       <c r="G7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -1534,10 +1591,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -1563,10 +1618,8 @@
       <c r="G9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -1599,10 +1652,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -1628,10 +1679,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -1657,10 +1706,8 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -1685,6 +1732,7 @@
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="C16" s="18" t="inlineStr">
         <is>
@@ -1693,14 +1741,19 @@
       </c>
       <c r="D16" s="19">
         <f>COUNTIF(F5:F14,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>de 8</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -1708,6 +1761,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
@@ -1724,7 +1778,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1739,16 +1803,16 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Revisión FIFO — Caducidades</t>
@@ -1762,10 +1826,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1790,7 +1855,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1807,10 +1872,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -1836,10 +1899,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -1865,10 +1926,8 @@
       <c r="G7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -1894,10 +1953,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -1923,10 +1980,8 @@
       <c r="G9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -1959,10 +2014,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -1988,10 +2041,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -2017,10 +2068,8 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -2045,6 +2094,7 @@
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="C16" s="18" t="inlineStr">
         <is>
@@ -2053,14 +2103,19 @@
       </c>
       <c r="D16" s="19">
         <f>COUNTIF(F5:F14,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>de 8</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -2068,6 +2123,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
@@ -2084,7 +2140,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -2099,16 +2165,16 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mantenimiento Mensual</t>
@@ -2122,10 +2188,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2150,7 +2217,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2167,10 +2234,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -2196,10 +2261,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -2225,10 +2288,8 @@
       <c r="G7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -2254,10 +2315,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -2283,10 +2342,8 @@
       <c r="G9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -2319,10 +2376,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -2348,10 +2403,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -2377,10 +2430,8 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -2405,6 +2456,7 @@
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="C16" s="18" t="inlineStr">
         <is>
@@ -2413,14 +2465,19 @@
       </c>
       <c r="D16" s="19">
         <f>COUNTIF(F5:F14,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>de 8</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -2428,6 +2485,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
@@ -2444,7 +2502,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
@@ -16,8 +16,11 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Limpieza Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'FIFO Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mantenimiento Mensual'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1436,7 +1439,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1788,8 +1791,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1798,7 +1809,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2150,8 +2161,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2160,7 +2179,7 @@
   <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2512,7 +2531,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/05-tareas-semanales-mensuales.xlsx
@@ -12,16 +12,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Limpieza Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'FIFO Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mantenimiento Mensual'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Trimestral y Anual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Trimestral y Anual'!$A$1:$G$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,8 +100,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -128,8 +146,13 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -151,11 +174,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +265,51 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,65 +686,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Tareas Semanales, Mensuales e Inventarios — Hamburguesería</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists periódicos + inventario diario de producción.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Trimestral, anual y vida útil en congelación</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Inventario Diario: parrillero/cocinero al inicio del turno</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• Limpieza, FIFO, mantenimiento según frecuencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = pendiente · ✓ = completada</t>
+    <row r="6" ht="48" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge el mantenimiento que se CONTRATA y que se pide en una inspección: DDD, conductos de extracción, extintores y BIE, instalación de gas, frigorista, aceite usado por gestor autorizado, legionela, agua, seguro y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>▸ Anota el número de parte en la columna verde y firma cuando la empresa haya venido; la última tarea de la hoja es apuntar la fecha de la próxima revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>▸ En la hoja mensual quedan las comprobaciones que hace tu propio equipo (filtros de campana, vista del extintor): no sustituyen a la revisión contratada, la preparan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «FIFO Semanal» tienes una tabla editable de vida útil en congelación por familia: una regla única para todo el congelador o tiras patatas buenas o sirves bacon rancio.</t>
         </is>
       </c>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 05-tareas-semanales-mensuales.xlsx: lo que NO es diario (semanal, mensual, trimestral y anual). El día a día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="35" customHeight="1">
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1647,6 @@
       </c>
       <c r="F38" s="8" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -1441,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1463,7 +1708,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1736,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1506,288 +1751,347 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  COCINA</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Desmontar y limpiar plancha a fondo</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Limpiar freidora interior (desmontar cestas)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Limpiar interior cámaras</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Desmontar campana y limpiar filtros</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Limpiar detrás y debajo de equipos</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA Y BAÑOS</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Limpiar cristales</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Fregar suelos con desengrasante</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Limpieza profunda baños</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
     <row r="16">
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D16" s="19">
-        <f>COUNTIF(F5:F14,"✓")</f>
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D21" s="19">
+        <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F16">
-        <f>COUNTIF(B5:B14,"?*")</f>
+      <c r="F21">
+        <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
         <v>8.0</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G14">
+  <conditionalFormatting sqref="A5:G19">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1811,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1833,7 +2137,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1861,7 +2165,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1876,288 +2180,603 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CÁMARAS</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Verificar fecha de carne (fresca max 3 días)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Revisar quesos abiertos</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Revisar salsas caseras (max 5 días)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Rotar: antiguo delante</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Desechar caducado</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Comprobar que ningún producto congelado supera su vida útil (ver la tabla al pie de esta hoja)</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Cámara</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Cocinero</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ALMACÉN</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Revisar pan: fecha, frescura</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>Revisar stock packaging</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Verificar aceite freidora: test polares</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
     <row r="16">
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D16" s="19">
-        <f>COUNTIF(F5:F14,"✓")</f>
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D22" s="19">
+        <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F16">
-        <f>COUNTIF(B5:B14,"?*")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL ORIENTATIVA EN CONGELACIÓN A −18 °C — ajústala a tu producto y a tu proveedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="36" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="n"/>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>Patties y carne picada cruda</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>3-4 meses</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>Congélalos ya porcionados y separados con papel: la picada tiene mucha superficie expuesta y se enrancia antes que la pieza entera</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="36" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>Bacon y panceta</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>1-2 meses</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>La grasa se enrancia aunque esté congelada: es lo primero que sabe a viejo</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="36" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="n"/>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>Pollo crudo (crispy, tenders, nuggets)</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>3-6 meses</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>Del congelador a la freidora, sin descongelar: si se atempera suelta agua y el rebozado se despega</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+      <c r="G30" s="36" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>Pan de burger (brioche, pretzel, sésamo)</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>Congélalo el día que llega, no cuando ya se está pasando; descongela a temperatura ambiente dentro de su bolsa</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="n"/>
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="36" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="n"/>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>Patatas prefritas congeladas</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>6-12 meses</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
+        <is>
+          <t>NUNCA se descongelan: van del congelador al aceite o quedan blandas y salpican</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="35" t="n"/>
+      <c r="G32" s="36" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="n"/>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>Aros de cebolla y rebozados</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>6 meses</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>Igual que las patatas: directos al aceite</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="36" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="n"/>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>Queso en lonchas</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="inlineStr">
+        <is>
+          <t>Se vuelve quebradizo al descongelar pero funde igual: úsalo sólo para fundir, no en frío</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+      <c r="G34" s="36" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="n"/>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>Salsas caseras y fondos</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>Etiquetar con fecha de producción Y de congelación: la vida útil de esta tabla se cuenta desde la de congelación</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="35" t="n"/>
+      <c r="G35" s="36" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="n"/>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>Verdura escaldada (cebolla, pimiento)</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>8-12 meses</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="inlineStr">
+        <is>
+          <t>Sin escaldar previamente, la mitad</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="n"/>
+      <c r="F36" s="35" t="n"/>
+      <c r="G36" s="36" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="18">
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="D31:G31"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D36:G36"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G14">
+  <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2181,7 +2800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2203,7 +2822,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2850,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2246,288 +2865,896 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPOS</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Revisión plancha: superficie, termostato</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Cambio completo aceite freidora</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Lavavajillas: filtros, sal</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Campana: motor, filtros</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Campana: motor y filtros; la limpieza de los CONDUCTOS de extracción por empresa homologada está en la hoja «Trimestral y Anual»</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Climatización: filtros</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SEGURIDAD</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Extintor: presión, caducidad</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Extintor: comprobación visual del usuario (aguja en zona verde, precinto intacto, acceso libre); la revisión oficial la hace el mantenedor y está en la hoja «Trimestral y Anual»</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Botiquín: stock, caducidades</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Salidas emergencia despejadas</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
     <row r="16">
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D16" s="19">
-        <f>COUNTIF(F5:F14,"✓")</f>
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D21" s="19">
+        <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F16">
-        <f>COUNTIF(B5:B14,"?*")</f>
+      <c r="F21">
+        <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
         <v>8.0</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G14">
+  <conditionalFormatting sqref="A5:G19">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Nº de parte</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTRATADO — EMPRESA AUTORIZADA</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Control de plagas (DDD): visita de la empresa autorizada, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Empresa DDD</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Limpieza de la campana y de los CONDUCTOS de extracción por empresa homologada: plancha y freidora juntas engrasan el conducto el doble de rápido</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Empresa externa</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Revisión de extintores y BIE por empresa mantenedora (etiqueta y acta de revisión)</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Mantenedor</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Retimbrado de extintores: prueba de presión cada 5 años desde su fabricación</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Mantenedor</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Revisión periódica de la instalación de gas por empresa habilitada (plancha, freidora y cocina de gas)</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Instalador gas</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Revisión de los equipos de frío por frigorista (estanqueidad y gas refrigerante)</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Frigorista</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AGUA, RESIDUOS Y ACEITE USADO</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Retirada del aceite usado de fritura por gestor autorizado y archivo de los documentos de entrega: en una hamburguesería es el residuo que más volumen genera</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Gestor autorizado</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Revisar el contrato de residuos y la retirada de cartón y envases: el delivery multiplica el volumen de envase</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Prevención de legionela si hay torre de refrigeración o agua caliente sanitaria de riesgo</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Empresa autorizada</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Analítica del agua de consumo si el local tiene depósito propio o descalcificador</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>Laboratorio</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADMINISTRACIÓN Y EQUIPOS</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="26" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Revisar la póliza del local (continente, contenido y responsabilidad civil) y su vencimiento</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Revisión del TPV y del software de facturación (requisitos antifraude / Verifactu), también el de las apps de delivery</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Calibrar los termómetros y la sonda de la plancha contra un patrón conocido: de esa sonda depende el núcleo de la carne picada</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Anotar la fecha de la próxima revisión de cada contrato y archivar el parte firmado</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="19">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Firma encargado/a: _________________________    Hora: _________</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A28:C28"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
